--- a/EIANN/data/supplementary_tables/Table_S6_mnist_hyperparams_part3.xlsx
+++ b/EIANN/data/supplementary_tables/Table_S6_mnist_hyperparams_part3.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>BTSP</t>
+          <t>Sup. BTSP</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">

--- a/EIANN/data/supplementary_tables/Table_S6_mnist_hyperparams_part3.xlsx
+++ b/EIANN/data/supplementary_tables/Table_S6_mnist_hyperparams_part3.xlsx
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Winit (H1)</t>
+          <t>W_init (H1)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BTSP Wmax (H1)</t>
+          <t>BTSP W_max (H1)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H1)</t>
+          <t>Y_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -585,7 +585,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H1)</t>
+          <t>Y_init (DendI, H1)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -629,7 +629,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bscale (H1)</t>
+          <t>B_scale (H1)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -659,7 +659,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H1)</t>
+          <t>W_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -681,7 +681,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H1)</t>
+          <t>Q_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -703,7 +703,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H1)</t>
+          <t>R_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -747,7 +747,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Qsum (DendI, H1)</t>
+          <t>Q_sum (DendI, H1)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rsum (DendI, H1)</t>
+          <t>R_sum (DendI, H1)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -813,7 +813,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Winit (H2)</t>
+          <t>W_init (H2)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BTSP Wmax (H2)</t>
+          <t>BTSP W_max (H2)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -909,7 +909,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H2)</t>
+          <t>Y_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -931,7 +931,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H2)</t>
+          <t>Y_init (DendI, H2)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -975,7 +975,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bscale (H2)</t>
+          <t>B_scale (H2)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1005,7 +1005,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H2)</t>
+          <t>W_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1027,7 +1027,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H2)</t>
+          <t>Q_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1049,7 +1049,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H2)</t>
+          <t>R_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1093,7 +1093,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Qsum (DendI, H2)</t>
+          <t>Q_sum (DendI, H2)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1137,7 +1137,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rsum (DendI, H2)</t>
+          <t>R_sum (DendI, H2)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1159,7 +1159,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Winit (Output)</t>
+          <t>W_init (Output)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1229,7 +1229,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BTSP Wmax (Output)</t>
+          <t>BTSP W_max (Output)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1255,7 +1255,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, Output)</t>
+          <t>Y_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1277,7 +1277,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Winit (SomaI, Output)</t>
+          <t>W_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1299,7 +1299,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, Output)</t>
+          <t>Q_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1321,7 +1321,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, Output)</t>
+          <t>R_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1343,7 +1343,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Binit (H1)</t>
+          <t>B_init (H1)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Binit (H2)</t>
+          <t>B_init (H2)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bsum (H1)</t>
+          <t>B_sum (H1)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bsum (H2)</t>
+          <t>B_sum (H2)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
